--- a/test-real-data/costo_transporte.xlsx
+++ b/test-real-data/costo_transporte.xlsx
@@ -145,12 +145,16 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="22" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="22" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -351,319 +355,319 @@
   <sheetFormatPr defaultColWidth="9.11328125" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="0" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>681</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>603</v>
       </c>
-      <c r="D2" s="1" t="n">
+      <c r="D2" s="2" t="n">
         <v>961</v>
       </c>
-      <c r="E2" s="1" t="n">
+      <c r="E2" s="2" t="n">
         <v>567</v>
       </c>
-      <c r="F2" s="1" t="n">
+      <c r="F2" s="2" t="n">
         <v>540</v>
       </c>
-      <c r="G2" s="1" t="n">
+      <c r="G2" s="2" t="n">
         <v>490</v>
       </c>
-      <c r="H2" s="1" t="n">
+      <c r="H2" s="2" t="n">
         <v>784</v>
       </c>
-      <c r="I2" s="1" t="n">
+      <c r="I2" s="2" t="n">
         <v>931</v>
       </c>
-      <c r="J2" s="1" t="n">
+      <c r="J2" s="2" t="n">
         <v>424</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>693</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>499</v>
       </c>
-      <c r="D3" s="1" t="n">
+      <c r="D3" s="2" t="n">
         <v>742</v>
       </c>
-      <c r="E3" s="1" t="n">
+      <c r="E3" s="2" t="n">
         <v>619</v>
       </c>
-      <c r="F3" s="1" t="n">
+      <c r="F3" s="2" t="n">
         <v>540</v>
       </c>
-      <c r="G3" s="1" t="n">
+      <c r="G3" s="2" t="n">
         <v>659</v>
       </c>
-      <c r="H3" s="1" t="n">
+      <c r="H3" s="2" t="n">
         <v>949</v>
       </c>
-      <c r="I3" s="1" t="n">
+      <c r="I3" s="2" t="n">
         <v>432</v>
       </c>
-      <c r="J3" s="1" t="n">
+      <c r="J3" s="2" t="n">
         <v>996</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>415</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>1559</v>
       </c>
-      <c r="D4" s="1" t="n">
+      <c r="D4" s="2" t="n">
         <v>565</v>
       </c>
-      <c r="E4" s="1" t="n">
+      <c r="E4" s="2" t="n">
         <v>492</v>
       </c>
-      <c r="F4" s="1" t="n">
+      <c r="F4" s="2" t="n">
         <v>701</v>
       </c>
-      <c r="G4" s="1" t="n">
+      <c r="G4" s="2" t="n">
         <v>846</v>
       </c>
-      <c r="H4" s="1" t="n">
+      <c r="H4" s="2" t="n">
         <v>1134</v>
       </c>
-      <c r="I4" s="1" t="n">
+      <c r="I4" s="2" t="n">
         <v>519</v>
       </c>
-      <c r="J4" s="1" t="n">
+      <c r="J4" s="2" t="n">
         <v>1198</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>705</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>664</v>
       </c>
-      <c r="D5" s="1" t="n">
+      <c r="D5" s="2" t="n">
         <v>953</v>
       </c>
-      <c r="E5" s="1" t="n">
+      <c r="E5" s="2" t="n">
         <v>208</v>
       </c>
-      <c r="F5" s="1" t="n">
+      <c r="F5" s="2" t="n">
         <v>217</v>
       </c>
-      <c r="G5" s="1" t="n">
+      <c r="G5" s="2" t="n">
         <v>782</v>
       </c>
-      <c r="H5" s="1" t="n">
+      <c r="H5" s="2" t="n">
         <v>1069</v>
       </c>
-      <c r="I5" s="1" t="n">
+      <c r="I5" s="2" t="n">
         <v>817</v>
       </c>
-      <c r="J5" s="1" t="n">
+      <c r="J5" s="2" t="n">
         <v>1137</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>622</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>450</v>
       </c>
-      <c r="D6" s="1" t="n">
+      <c r="D6" s="2" t="n">
         <v>786</v>
       </c>
-      <c r="E6" s="1" t="n">
+      <c r="E6" s="2" t="n">
         <v>192</v>
       </c>
-      <c r="F6" s="1" t="n">
+      <c r="F6" s="2" t="n">
         <v>742</v>
       </c>
-      <c r="G6" s="1" t="n">
+      <c r="G6" s="2" t="n">
         <v>1131</v>
       </c>
-      <c r="H6" s="1" t="n">
+      <c r="H6" s="2" t="n">
         <v>1119</v>
       </c>
-      <c r="I6" s="1" t="n">
+      <c r="I6" s="2" t="n">
         <v>937</v>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="J6" s="2" t="n">
         <v>1473</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>707</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>594</v>
       </c>
-      <c r="D7" s="1" t="n">
+      <c r="D7" s="2" t="n">
         <v>852</v>
       </c>
-      <c r="E7" s="1" t="n">
+      <c r="E7" s="2" t="n">
         <v>119</v>
       </c>
-      <c r="F7" s="1" t="n">
+      <c r="F7" s="2" t="n">
         <v>480</v>
       </c>
-      <c r="G7" s="1" t="n">
+      <c r="G7" s="2" t="n">
         <v>987</v>
       </c>
-      <c r="H7" s="1" t="n">
+      <c r="H7" s="2" t="n">
         <v>833</v>
       </c>
-      <c r="I7" s="1" t="n">
+      <c r="I7" s="2" t="n">
         <v>1045</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>1328</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>715</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>818</v>
       </c>
-      <c r="D8" s="1" t="n">
+      <c r="D8" s="2" t="n">
         <v>677</v>
       </c>
-      <c r="E8" s="1" t="n">
+      <c r="E8" s="2" t="n">
         <v>962</v>
       </c>
-      <c r="F8" s="1" t="n">
+      <c r="F8" s="2" t="n">
         <v>880</v>
       </c>
-      <c r="G8" s="1" t="n">
+      <c r="G8" s="2" t="n">
         <v>985</v>
       </c>
-      <c r="H8" s="1" t="n">
+      <c r="H8" s="2" t="n">
         <v>1215</v>
       </c>
-      <c r="I8" s="1" t="n">
+      <c r="I8" s="2" t="n">
         <v>259</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>772</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>566</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>629</v>
       </c>
-      <c r="D9" s="1" t="n">
+      <c r="D9" s="2" t="n">
         <v>518</v>
       </c>
-      <c r="E9" s="1" t="n">
+      <c r="E9" s="2" t="n">
         <v>798</v>
       </c>
-      <c r="F9" s="1" t="n">
+      <c r="F9" s="2" t="n">
         <v>715</v>
       </c>
-      <c r="G9" s="1" t="n">
+      <c r="G9" s="2" t="n">
         <v>889</v>
       </c>
-      <c r="H9" s="1" t="n">
+      <c r="H9" s="2" t="n">
         <v>1128</v>
       </c>
-      <c r="I9" s="1" t="n">
+      <c r="I9" s="2" t="n">
         <v>337</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>948</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>694</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>800</v>
       </c>
-      <c r="D10" s="1" t="n">
+      <c r="D10" s="2" t="n">
         <v>611</v>
       </c>
-      <c r="E10" s="1" t="n">
+      <c r="E10" s="2" t="n">
         <v>947</v>
       </c>
-      <c r="F10" s="1" t="n">
+      <c r="F10" s="2" t="n">
         <v>881</v>
       </c>
-      <c r="G10" s="1" t="n">
+      <c r="G10" s="2" t="n">
         <v>1089</v>
       </c>
-      <c r="H10" s="1" t="n">
+      <c r="H10" s="2" t="n">
         <v>1311</v>
       </c>
-      <c r="I10" s="1" t="n">
+      <c r="I10" s="2" t="n">
         <v>120</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>935</v>
       </c>
     </row>
